--- a/docs/downloads/经营分_河南省区__河南中片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_河南省区__河南中片区_2026-10-18.xlsx
@@ -878,14 +878,14 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I4" t="n">
-        <v>-20</v>
+        <v>-23</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -913,7 +913,7 @@
         <v>30</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T4" t="n">
         <v>20</v>
@@ -1053,7 +1053,7 @@
         <v>82</v>
       </c>
       <c r="I6" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>92</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2698,34 +2698,34 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>开封市</t>
+          <t>濮阳市</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>7572436305854875690</t>
+          <t>7304252013800327168</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>维也纳酒店(开封宋城路市政府店)</t>
+          <t>维也纳酒店(濮阳台前建德商业步行街店)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>维也纳酒店(开封宋城路市政府店)</t>
+          <t>维也纳酒店(建德商业步行街店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>10</v>
       </c>
       <c r="M25" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N25" t="n">
         <v>30</v>
@@ -2751,7 +2751,7 @@
         <v>30</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R25" t="n">
         <v>30</v>
@@ -2786,34 +2786,34 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>濮阳市</t>
+          <t>开封市</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>7304252013800327168</t>
+          <t>7145033722961692680</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>维也纳酒店(濮阳台前建德商业步行街店)</t>
+          <t>麗枫酒店（开封祥符店）</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>维也纳酒店(建德商业步行街店)</t>
+          <t>麗枫酒店(开封祥符区店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>97</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N26" t="n">
         <v>30</v>
@@ -2839,7 +2839,7 @@
         <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R26" t="n">
         <v>30</v>
@@ -2874,31 +2874,31 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>开封市</t>
+          <t>濮阳市</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>7145033722961692680</t>
+          <t>7593873984861669426</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>麗枫酒店（开封祥符店）</t>
+          <t>7天酒店智选版（濮阳清丰文化路北欧小镇店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>麗枫酒店(开封祥符区店)</t>
+          <t>7天酒店(清丰店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2915,19 +2915,19 @@
         <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N27" t="n">
         <v>30</v>
       </c>
       <c r="O27" t="n">
+        <v>20</v>
+      </c>
+      <c r="P27" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q27" t="n">
         <v>25</v>
-      </c>
-      <c r="P27" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>20</v>
       </c>
       <c r="R27" t="n">
         <v>30</v>
@@ -2962,27 +2962,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>濮阳市</t>
+          <t>开封市</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7593873984861669426</t>
+          <t>6601140932567894030</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7天酒店智选版（濮阳清丰文化路北欧小镇店）</t>
+          <t>7天酒店（开封清明上河园大梁门店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>7天酒店(清丰店)</t>
+          <t>7天连锁酒店(开封清明上河园大梁门店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3009,13 +3009,13 @@
         <v>30</v>
       </c>
       <c r="O28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P28" t="n">
         <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R28" t="n">
         <v>30</v>
@@ -3055,33 +3055,33 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>6601140932567894030</t>
+          <t>7537133444854188084</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7天酒店（开封清明上河园大梁门店）</t>
+          <t>凯里亚德酒店(开封清明上河园万岁山武侠城鼓楼夜市店)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7天连锁酒店(开封清明上河园大梁门店)</t>
+          <t>凯里亚德酒店(开封清明上河园鼓楼夜市店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -3091,19 +3091,19 @@
         <v>10</v>
       </c>
       <c r="M29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="N29" t="n">
         <v>30</v>
       </c>
       <c r="O29" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P29" t="n">
         <v>30</v>
       </c>
       <c r="Q29" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R29" t="n">
         <v>30</v>
@@ -3143,33 +3143,33 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7537133444854188084</t>
+          <t>7572436305854875690</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(开封清明上河园万岁山武侠城鼓楼夜市店)</t>
+          <t>维也纳酒店(开封宋城路市政府店)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(开封清明上河园鼓楼夜市店)</t>
+          <t>维也纳酒店(开封宋城路市政府店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H30" t="n">
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>-5</v>
+        <v>8</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>稳房源</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -3179,19 +3179,19 @@
         <v>10</v>
       </c>
       <c r="M30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="N30" t="n">
         <v>30</v>
       </c>
       <c r="O30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P30" t="n">
         <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R30" t="n">
         <v>30</v>
@@ -3231,17 +3231,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>7027850995514214435</t>
+          <t>7392887674106824738</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0开封河南大学鼓楼广场店）</t>
+          <t>维也纳酒店（5.0开封清明上河园河大店）</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>维也纳酒店(河南大学鼓楼广场店)</t>
+          <t>维也纳酒店(开封河南大学新校区店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3253,11 +3253,11 @@
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -3267,13 +3267,13 @@
         <v>10</v>
       </c>
       <c r="M31" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N31" t="n">
         <v>30</v>
       </c>
       <c r="O31" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P31" t="n">
         <v>30</v>
@@ -3319,17 +3319,17 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>7392887674106824738</t>
+          <t>7655918328065558554</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0开封清明上河园河大店）</t>
+          <t>锦江之星（开封北站博物馆店）</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>维也纳酒店(开封河南大学新校区店)</t>
+          <t>锦江之星(开封北站博物馆店)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3407,33 +3407,33 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>7655918328065558554</t>
+          <t>7656759304376027188</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>锦江之星（开封北站博物馆店）</t>
+          <t>白玉兰酒店（开封河南大学金明校区店）</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>锦江之星(开封北站博物馆店)</t>
+          <t>白玉兰酒店(开封河南大学金明校区店)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,附加分</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -3449,19 +3449,19 @@
         <v>30</v>
       </c>
       <c r="O33" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P33" t="n">
         <v>30</v>
       </c>
       <c r="Q33" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R33" t="n">
         <v>30</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="n">
         <v>20</v>
@@ -3490,38 +3490,38 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>濮阳市</t>
+          <t>开封市</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>7331980019956189225</t>
+          <t>7027850995514214435</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>锦江之星（濮阳水秀万达广场酒店）</t>
+          <t>维也纳酒店（5.0开封河南大学鼓楼广场店）</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>锦江之星(濮阳水秀万达广场酒店)</t>
+          <t>维也纳酒店(河南大学鼓楼广场店)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I34" t="n">
-        <v>-10</v>
+        <v>13</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -3531,7 +3531,7 @@
         <v>10</v>
       </c>
       <c r="M34" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N34" t="n">
         <v>30</v>
@@ -3543,7 +3543,7 @@
         <v>30</v>
       </c>
       <c r="Q34" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R34" t="n">
         <v>30</v>
@@ -3578,22 +3578,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>开封市</t>
+          <t>濮阳市</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>7656759304376027188</t>
+          <t>7042908084552861733</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>白玉兰酒店（开封河南大学金明校区店）</t>
+          <t>维也纳酒店（5.0濮阳中原路友谊店）</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>白玉兰酒店(开封河南大学金明校区店)</t>
+          <t>维也纳酒店(濮阳中原路友谊店)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>稳房源,附加分</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -3619,7 +3619,7 @@
         <v>10</v>
       </c>
       <c r="M35" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N35" t="n">
         <v>30</v>
@@ -3631,13 +3631,13 @@
         <v>30</v>
       </c>
       <c r="Q35" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="R35" t="n">
         <v>30</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="n">
         <v>20</v>
@@ -3671,17 +3671,17 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>7042908084552861733</t>
+          <t>7331980019956189225</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0濮阳中原路友谊店）</t>
+          <t>锦江之星（濮阳水秀万达广场酒店）</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>维也纳酒店(濮阳中原路友谊店)</t>
+          <t>锦江之星(濮阳水秀万达广场酒店)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3693,11 +3693,11 @@
         <v>105</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -3707,19 +3707,19 @@
         <v>10</v>
       </c>
       <c r="M36" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N36" t="n">
         <v>30</v>
       </c>
       <c r="O36" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P36" t="n">
         <v>30</v>
       </c>
       <c r="Q36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R36" t="n">
         <v>30</v>
@@ -3957,7 +3957,7 @@
         <v>110</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>120</v>
       </c>
       <c r="I48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
